--- a/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="373">
   <si>
     <t>id</t>
   </si>
@@ -2223,6 +2223,9 @@
 &lt;answer&gt;C&lt;/answer&gt;</t>
   </si>
   <si>
+    <t>&lt;answer&gt;(D) D. chair&lt;/answer&gt;</t>
+  </si>
+  <si>
     <t>To determine which object (lamp, door, chair, pillow) is closest to the printer, we need to analyze the spatial relationships between these objects and the printer across the provided frames. Since the frames are uniformly sampled, we can infer the relative positions and distances by examining the images.
 ### Step 1: Identify the printer's location
 From the frames, the printer is consistently located on a white nightstand next to a bed (as seen in frame 2). This is a key reference point.
@@ -2439,6 +2442,22 @@
 Step 8: Determine which object is closest to the kettle.
 Based on the spatial reasoning, the kettle is likely located near the sink or stove. The pan is typically located near the stove, and the power strip is typically located near the sink. The laptop is typically located near the bed or dresser. Therefore, the pan is likely the closest to the kettle.
 &lt;answer&gt;(B) B. pan&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To determine which object (trash bin, microwave, window, refrigerator) is closest to the chair, I need to analyze the spatial relationships between these objects and the chair based on the provided frames. The chair is not explicitly visible in the frames, but its presence can be inferred from the context (e.g., a table or bench in some frames, which is typically paired with a chair).
+Given the frames, I can identify the locations of the objects in question:
+- The refrigerator is visible in the first frame, positioned on the left side of the scene.
+- The microwave is visible in the fifth frame, mounted above the stove.
+- The window is visible in the sixth frame, located above the sink.
+- The trash bin is visible in the fourth frame, positioned near the counter and table.
+To determine the proximity of each object to the chair, I need to infer the chair's position. Since the chair is not directly visible, I will use the spatial context from the frames to infer its position. The chair is likely located near the table, as tables are typically paired with chairs.
+Now, I will analyze the distances of each object to the inferred chair position:
+- The refrigerator is on the far left, away from the table.
+- The microwave is above the stove, which is near the left side of the scene.
+- The window is above the sink, which is on the left side of the scene.
+- The trash bin is near the table, which is likely where the chair is located.
+Based on this analysis, the trash bin is the closest to the chair, as it is positioned near the table where the chair is likely located.
+&lt;answer&gt;(A) A. trash bin&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To determine which object (counter, chair, table, trash bin) is closest to the sofa, we need to analyze the spatial relationships between these objects in the provided images. The images appear to show a kitchen and dining area with a sofa visible in one of the frames.
@@ -4135,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>10.37785363197327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4164,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>7.695970296859741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4193,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>7.768648147583008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4222,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>5.63255500793457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4251,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>3.340338945388794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4280,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>5.55074667930603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4309,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>3.503411054611206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4338,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>6.613209009170532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4367,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7.551118135452271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4396,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1.376784324645996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4425,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>5.148638725280762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4454,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>32.45576453208923</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4483,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2.428830623626709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4512,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2.387402534484863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4541,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>5.420904397964478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4570,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1.979305028915405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4599,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>4.260786294937134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4628,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>5.330710172653198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4657,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>1.763788223266602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4686,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2.335469722747803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4715,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>8.332985162734985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4744,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>5.709820508956909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4773,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>2.983091115951538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4802,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>8.20527720451355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4831,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>7.871778964996338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4860,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>3.037756204605103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4889,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>4.062021970748901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4918,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3.308350563049316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4947,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>3.773203611373901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4976,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1.951313257217407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -5005,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>2.612979173660278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5034,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>5.103595018386841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -5063,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>3.723592519760132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5092,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>32.48550701141357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5121,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>2.202035427093506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5150,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>1.768399238586426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5179,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>2.172166585922241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5208,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>4.318999052047729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5237,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>4.221901893615723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5266,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>3.769302129745483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5295,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>5.107318878173828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5324,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>3.290465116500854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5353,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>3.048336982727051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5382,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>1.979700326919556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5411,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>7.59575343132019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5440,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>6.585525751113892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5469,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>16.12234663963318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5498,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>3.944827795028687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5527,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>4.597876787185669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5556,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1.856241941452026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5585,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>4.730122804641724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5614,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>5.948463201522827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5643,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>3.386246204376221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5672,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>4.500473022460938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5701,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>3.053534984588623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5730,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>2.616790294647217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5759,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>1.845953464508057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5788,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>1.958329916000366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5817,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>2.311752557754517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5846,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>8.32490873336792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5875,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>9.231451988220215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5904,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>5.582897663116455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5933,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>9.418354749679565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5962,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>17.85218644142151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5991,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>2.553598642349243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -6020,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>3.973043441772461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -6049,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>3.692681789398193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6078,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>1.844943523406982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6107,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>1.734832048416138</v>
+        <v>26.07110500335693</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6136,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>1.798372983932495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6165,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>1.944178819656372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6194,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>2.990903854370117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6223,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>2.639923572540283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6252,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>3.337687253952026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6281,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>3.098931789398193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6310,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>1.063723564147949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6339,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>9.494880437850952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6368,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>2.27223539352417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6397,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>1.845581531524658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6426,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>1.625363826751709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6455,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>5.643935918807983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6484,7 +6503,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>1.490622997283936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6513,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1.363345623016357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6542,7 +6561,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>4.483355760574341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6571,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>1.868577241897583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6600,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>2.108904838562012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6629,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>1.748875141143799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6658,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>1.589457988739014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6687,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>2.325063228607178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6716,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>4.05980372428894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6745,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>2.416385889053345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6774,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>4.122536659240723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6803,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>2.657212972640991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6832,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>2.120405435562134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6861,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>1.976820707321167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6890,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>1.982776641845703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6919,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>1.779800653457642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6948,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>2.276423931121826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6977,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>4.695757627487183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -7006,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>2.377297878265381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -7035,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>6.136454105377197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -7064,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>2.182233572006226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -7093,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>2.697831392288208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -7122,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>4.461477518081665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -7151,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>2.76746654510498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7180,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>2.36645245552063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7209,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>1.736555337905884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7238,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>2.515949249267578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7267,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>2.53410816192627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7296,7 +7315,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>3.689248561859131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7325,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>2.881245851516724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7354,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>1.718497753143311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7383,7 +7402,7 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>2.41673755645752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7412,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>2.570105791091919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7441,7 +7460,7 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>3.526984453201294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7470,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>2.230217695236206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7499,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>2.164618492126465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7516,19 +7535,19 @@
         <v>218</v>
       </c>
       <c r="E119" t="s">
-        <v>219</v>
+        <v>315</v>
       </c>
       <c r="F119" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G119" t="s">
         <v>218</v>
       </c>
       <c r="H119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119">
-        <v>1.540366649627686</v>
+        <v>6.197497367858887</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7545,7 +7564,7 @@
         <v>215</v>
       </c>
       <c r="E120" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F120" t="s">
         <v>218</v>
@@ -7557,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>2.506244659423828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7574,7 +7593,7 @@
         <v>217</v>
       </c>
       <c r="E121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F121" t="s">
         <v>215</v>
@@ -7586,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>2.832108736038208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7615,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>2.927881240844727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7632,7 +7651,7 @@
         <v>218</v>
       </c>
       <c r="E123" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F123" t="s">
         <v>217</v>
@@ -7644,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>3.475682258605957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7673,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>2.83469295501709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7702,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>4.809841871261597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7719,7 +7738,7 @@
         <v>218</v>
       </c>
       <c r="E126" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F126" t="s">
         <v>218</v>
@@ -7731,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>2.444828271865845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7760,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>8.159742832183838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7777,7 +7796,7 @@
         <v>216</v>
       </c>
       <c r="E128" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G128" t="s">
         <v>216</v>
@@ -7786,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>0.947880744934082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7803,7 +7822,7 @@
         <v>215</v>
       </c>
       <c r="E129" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F129" t="s">
         <v>215</v>
@@ -7815,7 +7834,7 @@
         <v>1</v>
       </c>
       <c r="I129">
-        <v>4.497888326644897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7844,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>2.743391990661621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7873,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>3.976991653442383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7890,7 +7909,7 @@
         <v>216</v>
       </c>
       <c r="E132" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F132" t="s">
         <v>218</v>
@@ -7902,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>4.932424545288086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7931,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>5.149344921112061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7948,7 +7967,7 @@
         <v>217</v>
       </c>
       <c r="E134" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F134" t="s">
         <v>217</v>
@@ -7960,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="I134">
-        <v>2.213538408279419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7977,7 +7996,7 @@
         <v>217</v>
       </c>
       <c r="E135" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F135" t="s">
         <v>217</v>
@@ -7989,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="I135">
-        <v>5.073250770568848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -8006,7 +8025,7 @@
         <v>217</v>
       </c>
       <c r="E136" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F136" t="s">
         <v>217</v>
@@ -8018,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="I136">
-        <v>4.101288080215454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -8035,7 +8054,7 @@
         <v>216</v>
       </c>
       <c r="E137" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F137" t="s">
         <v>217</v>
@@ -8047,7 +8066,7 @@
         <v>0</v>
       </c>
       <c r="I137">
-        <v>2.835056304931641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -8064,7 +8083,7 @@
         <v>218</v>
       </c>
       <c r="E138" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F138" t="s">
         <v>216</v>
@@ -8076,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>2.584988832473755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -8093,7 +8112,7 @@
         <v>215</v>
       </c>
       <c r="E139" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F139" t="s">
         <v>218</v>
@@ -8105,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>8.74072265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8134,7 +8153,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>2.82586669921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -8151,7 +8170,7 @@
         <v>216</v>
       </c>
       <c r="E141" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F141" t="s">
         <v>216</v>
@@ -8163,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="I141">
-        <v>2.756258487701416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8180,7 +8199,7 @@
         <v>218</v>
       </c>
       <c r="E142" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F142" t="s">
         <v>216</v>
@@ -8192,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>3.168777704238892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8221,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>2.370345115661621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8238,19 +8257,19 @@
         <v>217</v>
       </c>
       <c r="E144" t="s">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="F144" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G144" t="s">
         <v>217</v>
       </c>
       <c r="H144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144">
-        <v>1.460655689239502</v>
+        <v>2.075395345687866</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8267,7 +8286,7 @@
         <v>215</v>
       </c>
       <c r="E145" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F145" t="s">
         <v>215</v>
@@ -8279,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>3.88136887550354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8296,7 +8315,7 @@
         <v>217</v>
       </c>
       <c r="E146" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F146" t="s">
         <v>218</v>
@@ -8308,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>2.52372670173645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8325,7 +8344,7 @@
         <v>217</v>
       </c>
       <c r="E147" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F147" t="s">
         <v>217</v>
@@ -8337,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>1.284090995788574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8354,7 +8373,7 @@
         <v>215</v>
       </c>
       <c r="E148" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F148" t="s">
         <v>215</v>
@@ -8366,7 +8385,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>3.249859809875488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8383,7 +8402,7 @@
         <v>216</v>
       </c>
       <c r="E149" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F149" t="s">
         <v>216</v>
@@ -8395,7 +8414,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>5.44972562789917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8424,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>2.89457893371582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8453,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>2.971144199371338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8470,7 +8489,7 @@
         <v>215</v>
       </c>
       <c r="E152" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F152" t="s">
         <v>217</v>
@@ -8482,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>5.681737661361694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8499,7 +8518,7 @@
         <v>218</v>
       </c>
       <c r="E153" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F153" t="s">
         <v>215</v>
@@ -8511,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>5.913575410842896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8528,7 +8547,7 @@
         <v>216</v>
       </c>
       <c r="E154" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F154" t="s">
         <v>217</v>
@@ -8540,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>4.223929643630981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8557,7 +8576,7 @@
         <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F155" t="s">
         <v>215</v>
@@ -8569,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>6.222434043884277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8598,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>6.532026767730713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8615,7 +8634,7 @@
         <v>217</v>
       </c>
       <c r="E157" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F157" t="s">
         <v>217</v>
@@ -8627,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="I157">
-        <v>5.747865438461304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8656,7 +8675,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>6.288243770599365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8685,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>8.299777507781982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8702,7 +8721,7 @@
         <v>217</v>
       </c>
       <c r="E160" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F160" t="s">
         <v>216</v>
@@ -8714,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>3.48949933052063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8743,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>6.457447528839111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8760,7 +8779,7 @@
         <v>217</v>
       </c>
       <c r="E162" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F162" t="s">
         <v>216</v>
@@ -8772,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>2.500437259674072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8789,7 +8808,7 @@
         <v>215</v>
       </c>
       <c r="E163" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F163" t="s">
         <v>215</v>
@@ -8801,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>5.04637885093689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8818,7 +8837,7 @@
         <v>217</v>
       </c>
       <c r="E164" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F164" t="s">
         <v>217</v>
@@ -8830,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>5.309364318847656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8847,7 +8866,7 @@
         <v>217</v>
       </c>
       <c r="E165" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F165" t="s">
         <v>216</v>
@@ -8859,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>3.424698829650879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8888,7 +8907,7 @@
         <v>1</v>
       </c>
       <c r="I166">
-        <v>1.478100538253784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8905,7 +8924,7 @@
         <v>218</v>
       </c>
       <c r="E167" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F167" t="s">
         <v>215</v>
@@ -8917,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>3.508220195770264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8946,7 +8965,7 @@
         <v>0</v>
       </c>
       <c r="I168">
-        <v>6.644207954406738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8963,7 +8982,7 @@
         <v>218</v>
       </c>
       <c r="E169" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F169" t="s">
         <v>218</v>
@@ -8975,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="I169">
-        <v>3.363280534744263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8992,7 +9011,7 @@
         <v>218</v>
       </c>
       <c r="E170" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F170" t="s">
         <v>218</v>
@@ -9004,7 +9023,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>3.926153898239136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -9021,7 +9040,7 @@
         <v>217</v>
       </c>
       <c r="E171" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F171" t="s">
         <v>217</v>
@@ -9033,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="I171">
-        <v>5.125774383544922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -9050,7 +9069,7 @@
         <v>216</v>
       </c>
       <c r="E172" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F172" t="s">
         <v>216</v>
@@ -9062,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>4.0621018409729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -9079,7 +9098,7 @@
         <v>217</v>
       </c>
       <c r="E173" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F173" t="s">
         <v>218</v>
@@ -9091,7 +9110,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>4.160502433776855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -9108,7 +9127,7 @@
         <v>216</v>
       </c>
       <c r="E174" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F174" t="s">
         <v>215</v>
@@ -9120,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>2.870865345001221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -9149,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="I175">
-        <v>8.419161558151245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -9166,7 +9185,7 @@
         <v>216</v>
       </c>
       <c r="E176" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F176" t="s">
         <v>217</v>
@@ -9178,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>2.3271803855896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -9207,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="I177">
-        <v>6.31574010848999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -9224,7 +9243,7 @@
         <v>217</v>
       </c>
       <c r="E178" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F178" t="s">
         <v>217</v>
@@ -9236,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="I178">
-        <v>3.282398700714111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -9265,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>8.385501146316528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -9282,7 +9301,7 @@
         <v>216</v>
       </c>
       <c r="E180" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F180" t="s">
         <v>216</v>
@@ -9294,7 +9313,7 @@
         <v>1</v>
       </c>
       <c r="I180">
-        <v>2.733859777450562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -9323,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>6.560595750808716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -9352,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>6.579697847366333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9369,7 +9388,7 @@
         <v>215</v>
       </c>
       <c r="E183" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F183" t="s">
         <v>218</v>
@@ -9381,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>6.002069473266602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9398,7 +9417,7 @@
         <v>218</v>
       </c>
       <c r="E184" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F184" t="s">
         <v>217</v>
@@ -9410,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>2.427164316177368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9427,7 +9446,7 @@
         <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F185" t="s">
         <v>217</v>
@@ -9439,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>4.334323644638062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9468,7 +9487,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>6.56084680557251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9485,7 +9504,7 @@
         <v>218</v>
       </c>
       <c r="E187" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F187" t="s">
         <v>217</v>
@@ -9497,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>3.455251216888428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9514,7 +9533,7 @@
         <v>218</v>
       </c>
       <c r="E188" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F188" t="s">
         <v>216</v>
@@ -9526,7 +9545,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>5.624212503433228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9543,7 +9562,7 @@
         <v>216</v>
       </c>
       <c r="E189" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F189" t="s">
         <v>217</v>
@@ -9555,7 +9574,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>4.775458574295044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9572,7 +9591,7 @@
         <v>216</v>
       </c>
       <c r="E190" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F190" t="s">
         <v>215</v>
@@ -9584,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>8.203790903091431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9601,7 +9620,7 @@
         <v>216</v>
       </c>
       <c r="E191" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F191" t="s">
         <v>217</v>
@@ -9613,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>3.036955118179321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9630,7 +9649,7 @@
         <v>218</v>
       </c>
       <c r="E192" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F192" t="s">
         <v>218</v>
@@ -9642,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="I192">
-        <v>4.786166906356812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9659,7 +9678,7 @@
         <v>215</v>
       </c>
       <c r="E193" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F193" t="s">
         <v>217</v>
@@ -9671,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>5.465745210647583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9688,7 +9707,7 @@
         <v>217</v>
       </c>
       <c r="E194" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F194" t="s">
         <v>215</v>
@@ -9700,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>4.001868486404419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9717,7 +9736,7 @@
         <v>215</v>
       </c>
       <c r="E195" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F195" t="s">
         <v>215</v>
@@ -9729,7 +9748,7 @@
         <v>1</v>
       </c>
       <c r="I195">
-        <v>5.054465293884277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9746,7 +9765,7 @@
         <v>215</v>
       </c>
       <c r="E196" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F196" t="s">
         <v>216</v>
@@ -9758,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>5.682140827178955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9775,7 +9794,7 @@
         <v>217</v>
       </c>
       <c r="E197" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F197" t="s">
         <v>218</v>
@@ -9787,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>8.940578937530518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9804,7 +9823,7 @@
         <v>216</v>
       </c>
       <c r="E198" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F198" t="s">
         <v>215</v>
@@ -9816,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>5.299302339553833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9845,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>8.494580745697021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9862,7 +9881,7 @@
         <v>216</v>
       </c>
       <c r="E200" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F200" t="s">
         <v>217</v>
@@ -9874,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="I200">
-        <v>3.452172994613647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9891,7 +9910,7 @@
         <v>218</v>
       </c>
       <c r="E201" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F201" t="s">
         <v>218</v>
@@ -9903,7 +9922,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>3.209481716156006</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
